--- a/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-cat2.xlsx
+++ b/LLM_Extraction_and_CrossCritique/interactive-table/runs/query-cat2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\runs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dhrub\OneDrive\Desktop\Mayo-CoRAL\LLM_Extraction_and_CrossCritique\interactive-table\runs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2665E094-DFF5-48F2-8B88-A53F24D02DEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D659B84-0528-4C35-89F1-3DC829CAF1C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30195" yWindow="1395" windowWidth="21600" windowHeight="11100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1148,13 +1148,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B101"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="88.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="205.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="88.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="205.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1162,7 +1162,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>56</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -1186,7 +1186,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>31</v>
       </c>
@@ -1202,7 +1202,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>71</v>
       </c>
@@ -1210,7 +1210,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>43</v>
       </c>
@@ -1218,7 +1218,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>35</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -1234,7 +1234,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>60</v>
       </c>
@@ -1258,7 +1258,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -1266,7 +1266,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -1274,7 +1274,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1282,7 +1282,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>74</v>
       </c>
@@ -1290,7 +1290,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>51</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>36</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>58</v>
       </c>
@@ -1322,7 +1322,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>76</v>
       </c>
@@ -1330,7 +1330,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>77</v>
       </c>
@@ -1338,7 +1338,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -1346,7 +1346,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>50</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -1362,7 +1362,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -1370,7 +1370,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>47</v>
       </c>
@@ -1378,7 +1378,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -1386,7 +1386,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>80</v>
       </c>
@@ -1394,7 +1394,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>7</v>
       </c>
@@ -1402,7 +1402,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>8</v>
       </c>
@@ -1410,7 +1410,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>81</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>48</v>
       </c>
@@ -1426,7 +1426,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>1</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>34</v>
       </c>
@@ -1450,7 +1450,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>3</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>33</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>9</v>
       </c>
@@ -1474,7 +1474,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>2</v>
       </c>
@@ -1482,7 +1482,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>74</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>82</v>
       </c>
@@ -1498,7 +1498,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>6</v>
       </c>
@@ -1506,7 +1506,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>83</v>
       </c>
@@ -1514,7 +1514,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>84</v>
       </c>
@@ -1522,7 +1522,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>61</v>
       </c>
@@ -1530,7 +1530,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>85</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -1546,7 +1546,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1554,7 +1554,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>28</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>86</v>
       </c>
@@ -1570,7 +1570,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>87</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -1586,7 +1586,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>11</v>
       </c>
@@ -1602,7 +1602,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>54</v>
       </c>
@@ -1610,7 +1610,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>13</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>41</v>
       </c>
@@ -1626,7 +1626,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>42</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>88</v>
       </c>
@@ -1642,7 +1642,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>89</v>
       </c>
@@ -1650,7 +1650,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>90</v>
       </c>
@@ -1658,7 +1658,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>30</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>62</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -1682,7 +1682,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>91</v>
       </c>
@@ -1698,7 +1698,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>63</v>
       </c>
@@ -1706,7 +1706,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>68</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>92</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>93</v>
       </c>
@@ -1730,7 +1730,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>29</v>
       </c>
@@ -1738,7 +1738,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>94</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>95</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>29</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>96</v>
       </c>
@@ -1770,7 +1770,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>10</v>
       </c>
@@ -1778,7 +1778,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>97</v>
       </c>
@@ -1786,7 +1786,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>98</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>99</v>
       </c>
@@ -1802,7 +1802,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>100</v>
       </c>
@@ -1810,7 +1810,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>55</v>
       </c>
@@ -1818,7 +1818,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>42</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>101</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>102</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>64</v>
       </c>
@@ -1850,7 +1850,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>103</v>
       </c>
@@ -1866,7 +1866,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>65</v>
       </c>
@@ -1874,7 +1874,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>104</v>
       </c>
@@ -1882,7 +1882,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>105</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>45</v>
       </c>
@@ -1898,7 +1898,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>52</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>53</v>
       </c>
@@ -1914,7 +1914,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>59</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>5</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>106</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>4</v>
       </c>
@@ -1954,7 +1954,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>37</v>
       </c>
